--- a/www/download/COUNTRY.EST.rpA2.xlsx
+++ b/www/download/COUNTRY.EST.rpA2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Estônia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.732069749249581</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.765421279197398</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.886257639375243</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.898319147140311</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.936829544846575</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1.08150198965166</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1.12067421581635</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1.05838024669571</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.884040373180654</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.804181745990278</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.803019327628949</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.795988246201261</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.729713971652249</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.680147068595328</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.717622186357779</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.633</t>
+          <t>5.44997700484698</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.619</t>
+          <t>5.23616046245464</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.617</t>
+          <t>5.20642100217528</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>4.86324418489825</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.579</t>
+          <t>4.69722394832282</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.573</t>
+          <t>4.04312178219932</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.578</t>
+          <t>4.33377671463696</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.585</t>
+          <t>3.37666520545883</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.594</t>
+          <t>2.97495589189446</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>2.70137627412802</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.608</t>
+          <t>3.06424347876715</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.646</t>
+          <t>3.204030620284</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.656</t>
+          <t>3.28785725506598</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>2.95065296189223</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.614</t>
+          <t>3.0328021180481</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>3.54545334419024</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.573</t>
+          <t>3.35102820617744</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.569</t>
+          <t>3.27380002029605</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.554</t>
+          <t>3.11714870840385</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>3.20151418116409</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.521</t>
+          <t>2.7241226118703</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>2.67363708936169</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>1.97031851896595</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.542</t>
+          <t>1.56489773957989</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>1.44259484931642</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.559</t>
+          <t>1.67193822958301</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>1.73513034780913</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.597</t>
+          <t>1.54564930754338</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>1.31794246864906</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.547</t>
+          <t>1.30354657694133</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1229.997</t>
+          <t>1.36727371179632</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1202.232</t>
+          <t>1.25869783816357</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1197.109</t>
+          <t>1.23672862766522</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1175.736</t>
+          <t>1.14184148481501</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1121.586</t>
+          <t>1.25755215270918</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1108.908</t>
+          <t>1.01483575962041</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1114.127</t>
+          <t>0.977424941893514</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1127.774</t>
+          <t>0.566247013575205</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1148.49</t>
+          <t>0.00969882472080674</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1152.113</t>
+          <t>0.280482723070103</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1185.772</t>
+          <t>0.350575002981816</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1259.874</t>
+          <t>0.322765102242649</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>1271.582</t>
+          <t>0.122483216887778</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1270.92</t>
+          <t>-0.0528576788120653</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1097.816</t>
+          <t>-0.0444291238288157</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1102.698</t>
+          <t>4403201540.65877</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1071.376</t>
+          <t>4165758614.53649</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1064.047</t>
+          <t>4228154550.70234</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1038.062</t>
+          <t>4207911822.64649</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>992.222</t>
+          <t>3893998041.95016</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>975.926</t>
+          <t>4137360587.15559</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>995.82</t>
+          <t>4420760194.4679</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1009.111</t>
+          <t>4612796530.12835</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1022.755</t>
+          <t>4860574297.39968</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1018.847</t>
+          <t>5230486118.37569</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1073.443</t>
+          <t>4983912994.46797</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1141.254</t>
+          <t>5088119130.012</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1140.255</t>
+          <t>4829432221.40031</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1141.369</t>
+          <t>4648770041.29761</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>952.965</t>
+          <t>3948937438.1899</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>750358928.752933</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>42.43</t>
+          <t>758490475.393204</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>756156502.207288</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>40.18</t>
+          <t>764877907.471566</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>39.17</t>
+          <t>728213110.873988</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>39.63</t>
+          <t>807595889.559732</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>39.19</t>
+          <t>817770540.062235</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>39.47</t>
+          <t>1024958880.35365</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>35.89</t>
+          <t>1193795099.733</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>1245398091.95202</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>1214780477.15044</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>40.91</t>
+          <t>1251516636.10941</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>38.33</t>
+          <t>1296301426.59062</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>1427094983.11206</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>38.97</t>
+          <t>1202077133.16544</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>49.58</t>
+          <t>19853981.5226097</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>50.53</t>
+          <t>16114047.447736</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>50.76</t>
+          <t>16249345.7691156</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>51.03</t>
+          <t>13313053.6081699</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>53.04</t>
+          <t>11867906.6748302</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>52.96</t>
+          <t>12114920.2262841</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>53.46</t>
+          <t>11713763.7286041</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>10334404.5425352</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>53.21</t>
+          <t>8309235.94028095</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>52.54</t>
+          <t>7481951.20383457</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>51.15</t>
+          <t>6341138.83209846</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>50.66</t>
+          <t>5480799.63970609</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>53.01</t>
+          <t>4236415.64351478</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>52.78</t>
+          <t>3745126.48420935</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>52.36</t>
+          <t>4153446.86515763</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>11594.7353558663</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>11114.9914166791</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7.82</t>
+          <t>10679.42851374</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>10047.4565900066</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>9527.76373451705</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>9382.56019140209</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>9354.0603680476</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>9463.52568990061</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>10.89</t>
+          <t>10485.1555814563</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>11921.0316473355</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>12777.9737008286</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>14051.7613974971</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>16001.5730926237</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>17114.6480883448</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>13771.2321621697</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>53.18</t>
+          <t>19207.4226430574</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>52.51</t>
+          <t>18116.1684703722</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>51.77</t>
+          <t>18084.3947788269</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>50.92</t>
+          <t>17775.9796857785</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>16971.990458208</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>50.07</t>
+          <t>18135.5468281755</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>50.44</t>
+          <t>18692.9025559809</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>51.26</t>
+          <t>19755.6647982975</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>22287.7462805065</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>52.43</t>
+          <t>26013.0539827782</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>54.31</t>
+          <t>26364.7867761564</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>53.83</t>
+          <t>28013.838817087</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>29807.882272393</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>54.29</t>
+          <t>31344.0289159728</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>24609.9785130084</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>43.57</t>
+          <t>4.33850727271121</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>4.13716833539566</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>4.04888376736428</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>3.77617621510672</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>47.02</t>
+          <t>3.76835511793134</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>46.55</t>
+          <t>3.22477909583087</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>46.26</t>
+          <t>3.33200651464128</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>45.57</t>
+          <t>2.53883027778843</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>2.0362576960364</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>44.28</t>
+          <t>1.95169806567925</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>2.26494528601573</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>42.81</t>
+          <t>2.32596437727155</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>2.20478338710204</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>1.91225519166841</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>41.75</t>
+          <t>2.0260383746118</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>967.099672186975</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>1096.7654687633</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>1131.4188948865</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>1154.97389298963</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>1224.4171558303</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>1215.66951007819</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>1571.23836316282</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>1519.36704465963</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>2041.95741456902</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>2529.5653232159</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2515.11453711442</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3133.10485768548</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3917.59063730745</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>4279.21714478719</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3781.46945619082</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.732069749249581</t>
+          <t>1272.01038947776</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.765421279197398</t>
+          <t>1323.71810714346</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.886257639375243</t>
+          <t>1330.09059315266</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.898319147140311</t>
+          <t>1379.64990525174</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.936829544846575</t>
+          <t>1374.76517061353</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.08150198965166</t>
+          <t>1550.68335168919</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.12067421581635</t>
+          <t>1543.54575368272</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.05838024669571</t>
+          <t>1904.06628160165</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884040373180654</t>
+          <t>2203.79379681188</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.804181745990278</t>
+          <t>2315.29669620497</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803019327628949</t>
+          <t>2174.68757098181</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.795988246201261</t>
+          <t>2103.74287643787</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729713971652249</t>
+          <t>2170.9955223637</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.680147068595328</t>
+          <t>2354.94221635654</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.717622186357779</t>
+          <t>2197.86062647263</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-732779570.639594</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-601334692.13934</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-437695207.532076</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-338062039.764126</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-188690298.931174</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>52339403.0799345</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>153809765.283333</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>412642196.59178</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>623876950.137013</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>462894388.677202</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>219594662.307811</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>344376110.53871</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>366341866.643615</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>439774013.947001</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>412562652.019567</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-753927681.67336</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-625138692.508221</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-481135812.150466</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-392581992.139393</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-243999746.085315</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-42968160.9528139</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>44573932.9413619</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>315665476.502248</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>491948575.880244</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>292374941.382155</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>51350893.3834053</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>176237034.608164</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>179138584.432048</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>223594949.605659</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>183624061.218249</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>21148111.0337666</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>23804000.3688811</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>43440604.6183896</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>54519952.3752675</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>55309447.1541406</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>95307564.0327484</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>109235832.341972</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>96976720.0895323</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>131928374.256769</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>170519447.295047</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>168243768.924406</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>168139075.930546</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>187203282.211568</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>216179064.341341</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>228938590.801318</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>6790.63671519127</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>6800.16274500728</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>6715.47280489239</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>6589.45106263762</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>6555.36853724879</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>6551.29460846946</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>6686.65026060044</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>6738.16740824796</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>6691.28587604737</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>6834.05677966175</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>7100.23593343404</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>6996.97386597114</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>6957.57038354412</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>6858.19269566345</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>6650.8105977545</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>6974.54181797875</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>6977.10359146047</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>6885.63547893652</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>6751.20483588755</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>6695.40728020695</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>6705.89545592991</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6796.41995069822</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6865.72680709576</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>6798.86365408876</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>6926.76636262653</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>7161.16677360578</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>7081.89720646927</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>7017.20906060356</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>6978.88039083903</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>6753.31547036527</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>2167.32849127726</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>523.62</t>
+          <t>2402.29795269921</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>520.64</t>
+          <t>3067.4347138352</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>486.32</t>
+          <t>3484.31085948467</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>469.72</t>
+          <t>3304.5635402525</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>404.31</t>
+          <t>3801.3332003363</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>433.38</t>
+          <t>4159.16409014369</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>337.67</t>
+          <t>4530.15671550546</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>297.5</t>
+          <t>5826.2280084372</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>270.14</t>
+          <t>6741.41451549769</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>306.42</t>
+          <t>8072.00373214941</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>320.4</t>
+          <t>10009.0881723028</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>328.79</t>
+          <t>11380.2511355507</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>295.07</t>
+          <t>13084.9625879172</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>303.28</t>
+          <t>9918.3978810616</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>354.55</t>
+          <t>1301854075.20632</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>335.1</t>
+          <t>1183796280.32851</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>327.38</t>
+          <t>1304879312.82015</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>311.71</t>
+          <t>1385207889.48357</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>320.15</t>
+          <t>1328768695.45365</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>272.41</t>
+          <t>1521554150.03378</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>267.36</t>
+          <t>1628405160.86823</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>197.03</t>
+          <t>1649078707.1142</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>156.49</t>
+          <t>1761451523.88384</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>144.26</t>
+          <t>1769366808.0838</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>167.19</t>
+          <t>1822937875.54232</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>173.51</t>
+          <t>1836008910.44416</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>154.56</t>
+          <t>1629567738.05664</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>131.79</t>
+          <t>1654406061.51166</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>130.35</t>
+          <t>1349132585.48597</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>136.73</t>
+          <t>2546.41826961884</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>125.87</t>
+          <t>3144.99158132517</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>123.67</t>
+          <t>3766.49048932949</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>114.18</t>
+          <t>4203.4508560095</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>125.76</t>
+          <t>3740.89327521901</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>101.48</t>
+          <t>4096.48530438498</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>97.74</t>
+          <t>4409.5318070429</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>56.62</t>
+          <t>5149.8336042185</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>6606.27502048523</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>28.05</t>
+          <t>7725.70451545724</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>35.06</t>
+          <t>9115.80558120576</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>32.28</t>
+          <t>11651.0849010892</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>13466.3510619339</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>13935.8799653936</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-4.44</t>
+          <t>8832.51443366737</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>4416.977</t>
+          <t>678092172.12265</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4320.92</t>
+          <t>791499661.576194</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>4249.814</t>
+          <t>1050186771.07894</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>4093.255</t>
+          <t>1247501094.51968</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>3877.98</t>
+          <t>1266321719.02244</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3839.125</t>
+          <t>1661147933.31011</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3926.292</t>
+          <t>1860627893.95956</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>4018.51</t>
+          <t>2255457387.82121</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>4038.525</t>
+          <t>2616294572.12626</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>4123.504</t>
+          <t>2502475261.87584</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>4351.841</t>
+          <t>2309413952.95971</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>4574.906</t>
+          <t>2566223973.16456</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>4600.482</t>
+          <t>2431105336.54752</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>4609.026</t>
+          <t>2254734084.4818</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>4147.631</t>
+          <t>1533212547.92427</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>4005.797</t>
+          <t>-379.089778341575</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3896.493</t>
+          <t>-742.693628625958</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3817.746</t>
+          <t>-699.055775494291</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>3653.192</t>
+          <t>-719.139996524834</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>3472.379</t>
+          <t>-436.329734966514</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3411.914</t>
+          <t>-295.152104048683</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3542.587</t>
+          <t>-250.367716899219</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>3627.156</t>
+          <t>-619.676888713043</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>3624.67</t>
+          <t>-780.047012048033</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>3676.039</t>
+          <t>-984.289999959545</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>3966.192</t>
+          <t>-1043.80184905636</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>4162.5</t>
+          <t>-1641.99672878638</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>4154.365</t>
+          <t>-2086.09992638326</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>4156.065</t>
+          <t>-850.91737747648</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>3637.532</t>
+          <t>1085.88344739423</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>4403.202</t>
+          <t>623761903.083666</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4165.759</t>
+          <t>392296618.752312</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>4228.155</t>
+          <t>254692541.741205</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>4207.912</t>
+          <t>137706794.963888</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>3893.998</t>
+          <t>62446976.4312068</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4137.361</t>
+          <t>-139593783.276328</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4420.76</t>
+          <t>-232222733.091332</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>4612.797</t>
+          <t>-606378680.70701</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>4860.574</t>
+          <t>-854843048.242426</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>5230.486</t>
+          <t>-733108453.792043</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>4983.913</t>
+          <t>-486476077.417387</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>5088.119</t>
+          <t>-730215062.720399</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>4829.432</t>
+          <t>-801537598.490875</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>4648.77</t>
+          <t>-600328022.970142</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>3948.937</t>
+          <t>-184079962.438293</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>1793.59452</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>2140.72685</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>2215.72546</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>2430.87755</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>2345.39238</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>2334.89037</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>2549.4012</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>2967.99712</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>3989.60685</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>4725.43966</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>5473.89979</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>6631.53529</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>8560.62565</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>9439.11782</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>7172.98768</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2658.033</t>
+          <t>0.013172964283351</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2555.859</t>
+          <t>0.0285166551022916</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2496.864</t>
+          <t>0.037228186077764</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2378.424</t>
+          <t>0.0510811448519347</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2186.019</t>
+          <t>0.0564013983447858</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2140.494</t>
+          <t>0.0611608754549612</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2212.18</t>
+          <t>0.0531496920886186</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2209.661</t>
+          <t>0.0705493568903215</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2286.632</t>
+          <t>0.0704057999493625</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2396.981</t>
+          <t>0.0626220500274083</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2415.506</t>
+          <t>0.0816446396825839</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2552.204</t>
+          <t>0.0751128481071348</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2592.553</t>
+          <t>0.0654781193183656</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2538.348</t>
+          <t>0.0467346551791664</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2209.743</t>
+          <t>0.0240859188951734</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>1978.1820783021</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>2362.18888529114</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>2442.55657145964</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2664.76063660272</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2648.09972342715</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>2575.89638618198</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>2771.60707940775</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>3248.67343257762</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>4366.19409573783</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>5336.24859621905</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>6151.02077167553</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>7459.21239006176</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>10097.8506948805</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>12308.5231619955</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>10312.433995032</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>750.359</t>
+          <t>2163.1993614518</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>758.49</t>
+          <t>2598.52951763284</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>756.157</t>
+          <t>2685.60327370236</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>764.878</t>
+          <t>2952.21889994261</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>728.213</t>
+          <t>2924.45257344085</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>807.596</t>
+          <t>2873.44566883691</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>817.771</t>
+          <t>3049.05306926796</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1024.959</t>
+          <t>3570.04041898114</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1193.795</t>
+          <t>4873.65566729071</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1245.398</t>
+          <t>6061.3972959849</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1214.78</t>
+          <t>6760.24191490913</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>1251.517</t>
+          <t>8225.85810822455</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>1296.301</t>
+          <t>11192.336567059</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>1427.095</t>
+          <t>13653.5984685896</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>1202.077</t>
+          <t>11402.7682049438</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>433.85</t>
+          <t>15075.3469067108</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>413.72</t>
+          <t>16688.5233172253</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>404.89</t>
+          <t>16250.6814097098</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>377.62</t>
+          <t>17142.8042501008</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>376.84</t>
+          <t>17576.1241710507</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>322.48</t>
+          <t>16366.7523337209</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>333.2</t>
+          <t>17744.8560943062</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>253.88</t>
+          <t>20493.0261604917</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>203.63</t>
+          <t>26825.4155126232</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>195.17</t>
+          <t>32943.4903503841</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>226.49</t>
+          <t>37326.934013361</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>232.6</t>
+          <t>45488.4342718116</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>220.48</t>
+          <t>58978.9093797376</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>191.23</t>
+          <t>66640.7588690546</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>202.6</t>
+          <t>62017.4964204802</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>19.854</t>
+          <t>2163.1993614518</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>16.114</t>
+          <t>2208.17303224124</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>16.249</t>
+          <t>2391.50829736382</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>13.313</t>
+          <t>2510.25849967421</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>11.868</t>
+          <t>2402.04956346056</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>12.115</t>
+          <t>2650.79965257279</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>11.714</t>
+          <t>2756.25269208334</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>10.334</t>
+          <t>2965.24729246084</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>8.309</t>
+          <t>3230.77354530927</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>7.482</t>
+          <t>3571.51776746887</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>6.341</t>
+          <t>3786.38739355488</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>5.481</t>
+          <t>4277.64375246507</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>4.236</t>
+          <t>4821.11516570349</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>3.745</t>
+          <t>5026.92452903273</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>4.153</t>
+          <t>4407.12130256491</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1978.1820783021</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2005.18503207527</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2168.92671235542</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2260.62913280164</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2155.34210301008</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2358.82577089619</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2495.2515529011</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2672.68244677767</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2870.10050861952</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>3131.02360572584</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>3435.76932676861</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>3880.8857756492</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>4346.26195458432</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>4509.60466212511</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>3940.57773726773</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1165.6866785482</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1572.66633236716</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1736.40228629764</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2030.64796005739</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2215.73513655915</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2216.67441116309</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2514.37200073204</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2965.13686101886</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>3930.62225270929</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>4592.5542240151</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>5562.65861509087</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>6549.87071177545</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>7779.41870294098</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>7393.65003141043</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>5275.21784505622</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>4005796598.29133</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>3896493252.88917</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>3817746289.58132</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>3653191669.12629</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>3472378714.18069</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>3411914232.09089</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3542587307.03132</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>3627155519.28362</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>3624669559.05486</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>3676039139.0154</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>3966191792.41626</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>4162499749.26263</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>4154365276.61429</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>4156064773.57205</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>3637531534.20196</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>4416977333.32594</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>4320920254.19147</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>4249814217.59962</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>4093255491.99862</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>3877979896.69587</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>3839125148.51987</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3926291804.37937</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>4018509900.19315</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>4038525010.52873</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>4123504016.55552</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>4351841048.32023</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>4574905595.37915</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>4600482260.79432</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>4609025729.29185</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>4147631232.07811</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2658032653.89877</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2555858945.57419</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2496863999.12794</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2378423699.84485</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2186018983.32026</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2140494307.13677</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2212179601.74322</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2209660819.35729</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2286632173.66386</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2396980784.70086</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2415506323.31016</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2552204160.37232</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2592552935.50933</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2538348325.09053</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2209743264.3613</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>633300</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>619300</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>617200</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>606300</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>579200</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>572500</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>577699.999832412</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>585300</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>594000</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>595300.000127613</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>607700</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>646000</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>655600.000094429</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>660424.806154005</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>614162.221545645</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>589900</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>573000</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>568500</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>554400</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>529700</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>520800</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>529799.999845246</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>538300.000508112</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>541700</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>537899.999595459</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>558600</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>594899.999484977</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>597100.00008625</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>606000</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>546930.555416823</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1229996614.94619</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1202231511.84761</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1197108626.34275</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1175735691.08207</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1121585837.85306</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>1108907704</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1114127481.65549</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1127773589</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>1148490171</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1152113319.26823</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>1185772206</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>1259874378</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>1271582452.36758</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>1270919798.47214</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1097815928.62376</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1102698335.57299</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1071375723.00998</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1064046584.46363</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1038061970.02459</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>992221810.700474</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>975925914</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>995819565.683451</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>1009110983</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>1022754578</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>1018847478.2451</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>1073443327</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>1141254371</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>1140254722.30617</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>1141368776</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>952964600.63245</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.432957307584914</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.424290485280814</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.414244980080208</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.401835231658574</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.391720262374542</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.396275348473721</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.391932582665419</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.39465875502121</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.358943598706702</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.396037207919124</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.41643028720111</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.409067485883032</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.38331425702095</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.372967861503811</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.389717279509351</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.495833562839275</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.505335916986218</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.507567636861314</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.510313637691528</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.530444633195852</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.529587032593355</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.534578002160968</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.533321226370326</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.532121704033019</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.525422647058035</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.511536690506456</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.506614254744889</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.530096368124594</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.527774495260558</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.523574013489296</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.0712091295758107</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.0703735977329677</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.0781873830584773</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.0878511306498983</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.0778351044296063</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.0741376189329238</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.0734894151736126</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.072020018608464</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.108934697260279</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.0785401450228414</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.0720330222924337</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.0843182593720788</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.0865893748544551</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.0992576432356307</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.0867087070013527</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.531829004552595</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.525089086452411</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.517666710432824</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.509186085967553</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.494162685057745</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.500674090550267</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.504438033180471</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.512588864937562</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.503765006341259</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.524337237871557</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.543064042950419</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.538267789634217</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.538045983770225</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.542869209762013</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.554975521217162</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.435723975581996</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.443049763377036</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.44686742156449</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.450995809736388</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.470217032886022</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.465455886730267</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.462643656485473</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.455677040208562</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.460037890308703</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.442799612485211</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.427497535090145</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.428050405386733</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.431646911661359</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.425993440753631</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.417506188124432</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.0324470198654085</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.031861150170553</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.0354658680026851</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.0398181042960591</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.0356202820562328</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.0338700227194656</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.0329183103340563</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.0317340948538765</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.0361971033500377</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.0328631496432316</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.0294384219594362</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.0336818049790499</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.0303071045684164</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.0311373494843565</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.0275182906584063</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>8283.83643</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>9788.73997</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>10859.83237</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>12316.32551</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>12179.36035</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>12772.51023</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>14048.57844</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>16424.78141</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>21205.70703</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>26063.58469</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>30167.77286</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>35532.43521</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>44246.99087</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>48445.03863</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>37266.24415</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>3328.88604</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>4171.19585</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>4422.00556</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>4982.86686</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>5140.18771</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>5090.12008</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>5563.42507</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>6535.17728</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>8804.27792</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>10653.95152</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>12322.90053</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>14775.72882</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>18971.75527</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>21047.2485</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>16677.98605</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>11036.205760143</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>11537.7600611927</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>12212.6441979157</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>13076.9889229306</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>13676.9054056121</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>14428.9055271773</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>15261.1881713661</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>16381.5870515466</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>17761.4481197441</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>19174.1289286297</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>20828.4374679303</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>22974.5590393707</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>25135.2373466103</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>26689.8456049247</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>27213.4780317637</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
